--- a/testakten/familienrecht-unterhalt-zugewinn-bad-nauheim/xlsx/rohdaten_unterhalt_zugewinn_neumann.xlsx
+++ b/testakten/familienrecht-unterhalt-zugewinn-bad-nauheim/xlsx/rohdaten_unterhalt_zugewinn_neumann.xlsx
@@ -8,10 +8,20 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Einkommen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kinderkosten" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vermoegen" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kinder" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vermögen" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fristen" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Einkommen'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Einkommen'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kinder'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Kinder'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Vermögen'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Vermögen'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Fristen'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Fristen'!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,7 +38,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00183941"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
@@ -40,7 +57,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F1F1"/>
+        <fgColor rgb="00E7EFF1"/>
       </patternFill>
     </fill>
   </fills>
@@ -54,7 +71,7 @@
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="00B6C7C7"/>
+        <color rgb="00C7D2D5"/>
       </bottom>
     </border>
   </borders>
@@ -63,10 +80,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -432,17 +449,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,22 +476,27 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Quelle</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Brutto</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Netto</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Sonderzahlung</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Nebeneinkunft</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Belegstatus</t>
+          <t>Beleg</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Prüfung</t>
         </is>
       </c>
     </row>
@@ -488,18 +511,25 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>4132.4</v>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>MVZ</t>
+        </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>6820</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>4124.18</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>vollständig</t>
+          <t>Abrechnung</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Bereitschaft</t>
         </is>
       </c>
     </row>
@@ -514,20 +544,23 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>4219.7</v>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>MVZ</t>
+        </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>6940</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>4197.64</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>vollständig</t>
-        </is>
-      </c>
+          <t>Abrechnung</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -540,18 +573,25 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>4861.9</v>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>MVZ</t>
+        </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>640</v>
+        <v>7890</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>300</v>
+        <v>4748.22</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>vollständig</t>
+          <t>Abrechnung</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Nachzahlung 640 netto</t>
         </is>
       </c>
     </row>
@@ -566,20 +606,23 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>4167.2</v>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>MVZ</t>
+        </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>7010</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>4231.47</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>vollständig</t>
-        </is>
-      </c>
+          <t>Abrechnung</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -592,20 +635,23 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>4111.8</v>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>MVZ</t>
+        </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>6630</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>600</v>
+        <v>3791.49</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>vollständig</t>
-        </is>
-      </c>
+          <t>Abrechnung</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -615,21 +661,30 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>5122.6</v>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>HydroMotion</t>
+        </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>27550</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>vollständig</t>
+          <t>Bonusmitteilung</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Abrechnung fehlt</t>
         </is>
       </c>
     </row>
@@ -641,21 +696,30 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>5122.6</v>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>MN Strömungstechnik</t>
+        </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>10400</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>vollständig</t>
+          <t>Rechnungen</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Kosten und Zufluss</t>
         </is>
       </c>
     </row>
@@ -667,70 +731,37 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>5122.6</v>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>MN Strömungstechnik</t>
+        </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>8500</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>vollständig</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Martin</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Screenshot unvollständig</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Martin</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n">
-        <v>4500</v>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Nebengewerbe streitig</t>
+          <t>Rechnung</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Zufluss offen</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -738,16 +769,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -776,6 +809,16 @@
           <t>Beleg</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Bezahlt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -785,20 +828,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Nachhilfe Mathematik</t>
+          <t>Lerntherapie</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>160</v>
+        <v>780</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>monatlich</t>
+          <t>einmalig/12 Einheiten</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>fehlt</t>
+          <t>Rechnung</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Elena geplant</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Zustimmung und Teilnahme</t>
         </is>
       </c>
     </row>
@@ -810,45 +863,65 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Musikschule</t>
+          <t>Klassenfahrt</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>86</v>
+        <v>410</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>monatlich</t>
+          <t>einmalig</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Lastschrift</t>
+          <t>Schulbrief</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Anzahlung Elena</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Rest</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Jakob</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Klassenfahrt</t>
+          <t>Kieferorthopädie</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>395</v>
+        <v>1260</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>einmalig</t>
+          <t>Behandlung</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Elternbrief</t>
+          <t>Kostenschätzung</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Plan</t>
         </is>
       </c>
     </row>
@@ -864,41 +937,57 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>monatlich</t>
+          <t>jährlich</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Vereinsbeleg</t>
-        </is>
-      </c>
+          <t>Verein</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Jakob</t>
+          <t>Clara</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Kieferorthopädie</t>
+          <t>Brille</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>42</v>
+        <v>286</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>monatlich</t>
+          <t>einmalig</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Plan fehlt</t>
+          <t>Anzahlung</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Endrechnung</t>
         </is>
       </c>
     </row>
@@ -923,37 +1012,24 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Gebührenbescheid</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Clara</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Brille</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>318.4</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>einmalig</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Rechnung</t>
+          <t>Bescheid</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Kostenbeteiligung</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -961,16 +1037,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -986,63 +1064,95 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Anfangswert</t>
+          <t>Wert</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Zwischenwert 18.06.2026</t>
+          <t>Schuld</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Belegstatus</t>
+          <t>Datum</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Beleg</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Elena</t>
+          <t>beide</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Depot MainInvest</t>
+          <t>Familienhaus</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>28500</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>42600</v>
+        <v>790000</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Anfangsstichtag offen</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Maklerspanne</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Darlehen und Zustand</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Elena</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Tagesgeld</t>
+          <t>TradePort</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
+        <v>126840.22</v>
+      </c>
+      <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>18200</v>
-      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Screenshot</t>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Jahresauszug</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Umsatz Juni</t>
         </is>
       </c>
     </row>
@@ -1054,114 +1164,225 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Depot TradePort</t>
+          <t>Grundstück Ober-Mörlen</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>86300</v>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Screenshot</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Eigenangabe</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Gutachten</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Elena</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Lebensversicherung</t>
+          <t>Schenkung Tante</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>54800</v>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Stand 01.01.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Martin</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Wiesengrundstück Ober-Mörlen</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Grundbuch fehlt</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Beide</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Familienhaus</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>760000-820000</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Maklerkurzbewertung</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Beide</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Hausdarlehen</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>-419800</v>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Bankunterlagen</t>
+          <t>2018-08-14</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Kontoauszug fehlt</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Zuwendung und Verwendung</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Vorgang</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Frist</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Vorfrist</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Verantwortlich</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Ergänzung Auskunft</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Feldmann</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Entwurf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Unterlagen Elena</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Mandantin</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Berechnung Arbeitsstand</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Kanzlei</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Hauslasten Juli</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>beide</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToWidth="1"/>
 </worksheet>
 </file>